--- a/Output/EB/tabla_min_max_pesos_111.xlsx
+++ b/Output/EB/tabla_min_max_pesos_111.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/florenciaruiz/BID 2/Paper Valerie/Nietos/México/Paper_nietos_mex/Output/EB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E533881-F4AC-0043-8ADC-23A16B5FA3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-8640" yWindow="-23140" windowWidth="25800" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>alternativa</t>
   </si>
@@ -78,8 +85,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -101,27 +108,370 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -135,230 +485,236 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1">
-        <v>2.4219682278156826e-05</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C2" s="2">
+        <v>2.4219682278156826E-5</v>
+      </c>
+      <c r="D2" s="2">
         <v>1.3157469034194946</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
-        <v>7.2662359295810092e-14</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3" s="2">
+        <v>7.2662359295810092E-14</v>
+      </c>
+      <c r="D3" s="2">
         <v>2.172307014465332</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1">
-        <v>8.7734614233094014e-13</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="C4" s="2">
+        <v>8.7734614233094014E-13</v>
+      </c>
+      <c r="D4" s="2">
         <v>2.0310039520263672</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1">
-        <v>3.367397926032375e-11</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5" s="2">
+        <v>3.367397926032375E-11</v>
+      </c>
+      <c r="D5" s="2">
         <v>1.7073675394058228</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="1">
-        <v>3.657074371957828e-07</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6" s="2">
+        <v>3.657074371957828E-7</v>
+      </c>
+      <c r="D6" s="2">
         <v>0.43873032927513123</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1">
-        <v>1.0970095174489638e-07</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="C7" s="2">
+        <v>1.0970095174489638E-7</v>
+      </c>
+      <c r="D7" s="2">
         <v>0.40213286876678467</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1">
-        <v>1.1848471796956716e-06</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="C8" s="2">
+        <v>1.1848471796956716E-6</v>
+      </c>
+      <c r="D8" s="2">
         <v>2.2734420299530029</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1">
-        <v>2.0240640768884445e-10</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="C9" s="2">
+        <v>2.0240640768884445E-10</v>
+      </c>
+      <c r="D9" s="2">
         <v>0.31954637169837952</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1">
-        <v>3.7837962914107374e-10</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10" s="2">
+        <v>3.7837962914107374E-10</v>
+      </c>
+      <c r="D10" s="2">
         <v>0.45039272308349609</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1">
-        <v>2.9114438473592836e-10</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="C11" s="2">
+        <v>2.9114438473592836E-10</v>
+      </c>
+      <c r="D11" s="2">
         <v>0.30050995945930481</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1">
-        <v>3.7817080430006176e-09</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="C12" s="2">
+        <v>3.7817080430006176E-9</v>
+      </c>
+      <c r="D12" s="2">
         <v>0.49199667572975159</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="1">
-        <v>7.5361223223370147e-11</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="C13" s="2">
+        <v>7.5361223223370147E-11</v>
+      </c>
+      <c r="D13" s="2">
         <v>0.40700116753578186</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="1">
-        <v>1.4708339127343397e-07</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="C14" s="2">
+        <v>1.4708339127343397E-7</v>
+      </c>
+      <c r="D14" s="2">
         <v>0.62313032150268555</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="1">
-        <v>1.3365409294653828e-07</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="C15" s="2">
+        <v>1.3365409294653828E-7</v>
+      </c>
+      <c r="D15" s="2">
         <v>0.37567448616027832</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="1">
-        <v>1.2027625178460451e-06</v>
-      </c>
-      <c r="D16" s="1">
+      <c r="C16" s="2">
+        <v>1.2027625178460451E-6</v>
+      </c>
+      <c r="D16" s="2">
         <v>0.62806129455566406</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="1">
-        <v>2.1381447203003597e-08</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="C17" s="2">
+        <v>2.1381447203003597E-8</v>
+      </c>
+      <c r="D17" s="2">
         <v>0.53162705898284912</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C2:D17">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Output/EB/tabla_min_max_pesos_111.xlsx
+++ b/Output/EB/tabla_min_max_pesos_111.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/florenciaruiz/BID 2/Paper Valerie/Nietos/México/Paper_nietos_mex/Output/EB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E533881-F4AC-0043-8ADC-23A16B5FA3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D3587D-2124-4047-B81B-DBFFF7712C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-8640" yWindow="-23140" windowWidth="25800" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1040" yWindow="1380" windowWidth="25800" windowHeight="17600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>alternativa</t>
   </si>
@@ -80,16 +81,39 @@
   </si>
   <si>
     <t>max_peso</t>
+  </si>
+  <si>
+    <t>Spanish Presence 1936-1955</t>
+  </si>
+  <si>
+    <t>Spanish Presence 1956-1978</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max </t>
+  </si>
+  <si>
+    <t>Alternative</t>
+  </si>
+  <si>
+    <t>Spanish Presence (Any Window)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -119,15 +143,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -711,6 +772,441 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:D17">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD86712F-ACB7-0447-A1B9-891A1BCEDC18}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2.4219682278156826E-5</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1.3157469034194946</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1.5341743574936122E-5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.92082375288009644</v>
+      </c>
+      <c r="F3" s="2">
+        <v>4.7445542287915992E-5</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1.7711659669876099</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>7.2662359295810092E-14</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2.172307014465332</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.2527585551731664E-37</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1.7357180118560791</v>
+      </c>
+      <c r="F4" s="2">
+        <v>8.7564795188234448E-20</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3.2468152046203613</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>8.7734614233094014E-13</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2.0310039520263672</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2.0961326737510981E-38</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1.5018461942672729</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1.4868259792458797E-19</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3.0744669437408447</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>3.367397926032375E-11</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1.7073675394058228</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2.0449744123229823E-39</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.4287285804748535</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8.2858585179537525E-18</v>
+      </c>
+      <c r="G6" s="2">
+        <v>2.4521636962890625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3.657074371957828E-7</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.43873032927513123</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2.9359572597415066E-8</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.47357165813446045</v>
+      </c>
+      <c r="F7" s="2">
+        <v>4.1957591351244233E-7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.62044697999954224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1.0970095174489638E-7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.40213286876678467</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.9030423710678134E-16</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.39198112487792969</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1.7283240056999917E-9</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.55051440000534058</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1.1848471796956716E-6</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2.2734420299530029</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5.0167830485142476E-16</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1.6762443780899048</v>
+      </c>
+      <c r="F9" s="2">
+        <v>7.7023583352944757E-8</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2.8911592960357666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2.0240640768884445E-10</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.31954637169837952</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1.018689786815897E-20</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.26064613461494446</v>
+      </c>
+      <c r="F10" s="2">
+        <v>4.0492332072661006E-12</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0.41718611121177673</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>3.7837962914107374E-10</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.45039272308349609</v>
+      </c>
+      <c r="D11" s="2">
+        <v>2.3816477543356642E-22</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.58534950017929077</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4.6134416092693984E-12</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0.83072930574417114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2.9114438473592836E-10</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.30050995945930481</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3.6297302302494729E-22</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.497149258852005</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2.994998791465441E-12</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0.40994349122047424</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3.7817080430006176E-9</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.49199667572975159</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3.770831457807844E-21</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.39009407162666321</v>
+      </c>
+      <c r="F13" s="2">
+        <v>5.0824783780087179E-11</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0.73038935661315918</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>7.5361223223370147E-11</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.40700116753578186</v>
+      </c>
+      <c r="D14" s="2">
+        <v>6.2338720962691963E-21</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0.31560167670249939</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1.4328226452396096E-12</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.51315802335739136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.4708339127343397E-7</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.62313032150268555</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2.0092734236677352E-17</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0.84056496620178223</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2.3200624953569065E-9</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1.1820071935653687</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.3365409294653828E-7</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.37567448616027832</v>
+      </c>
+      <c r="D16" s="2">
+        <v>9.0251441018479055E-18</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0.60182511806488037</v>
+      </c>
+      <c r="F16" s="2">
+        <v>9.8692422921253932E-10</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0.59528785943984985</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1.2027625178460451E-6</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.62806129455566406</v>
+      </c>
+      <c r="D17" s="2">
+        <v>5.1951561362021306E-16</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0.57095080614089966</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3.3227170299191682E-8</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.98046499490737915</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2.1381447203003597E-8</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.53162705898284912</v>
+      </c>
+      <c r="D18" s="2">
+        <v>5.3318401030910172E-16</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.47011843323707581</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1.038753283461776E-9</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.72933179140090942</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B3:C18">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E18">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>0.5</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.5</formula>
     </cfRule>
